--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chr1sren/Documents/CodeCourse/sta380_repo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasmi\Desktop\Study\2025-2026\Winter\sta380_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BB423E-DEBE-CB41-BB4B-94C5247AED6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C140A3-4321-491B-A505-69C46209DD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -88,9 +88,6 @@
     <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
   </si>
   <si>
-    <t>Team Cheryl</t>
-  </si>
-  <si>
     <t>Renfei Wu</t>
   </si>
   <si>
@@ -110,6 +107,21 @@
   </si>
   <si>
     <t>Robustness of models with different loss functions and estators under distribution shift</t>
+  </si>
+  <si>
+    <t>Team Chris</t>
+  </si>
+  <si>
+    <t>Shiqi Tian</t>
+  </si>
+  <si>
+    <t>tianshi8</t>
+  </si>
+  <si>
+    <t>https://github.com/Dream-ABC</t>
+  </si>
+  <si>
+    <t>Dream-ABC</t>
   </si>
 </sst>
 </file>
@@ -187,7 +199,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -404,17 +416,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -422,15 +434,15 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -438,76 +450,76 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -525,62 +537,77 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="D21">
         <v>1009998237</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
         <v>25</v>
       </c>
-      <c r="F21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22">
+        <v>1009834654</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>21</v>
       </c>

--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasmi\Desktop\Study\2025-2026\Winter\sta380_repo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4402EC5-426A-4CC4-A957-CB73C3690850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="14860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -50,12 +44,29 @@
     <t>Topic Number 1</t>
   </si>
   <si>
+    <t>permutation test comparing two distinct groups by using mean difference</t>
+  </si>
+  <si>
     <t>Simulated distributions, if applicable:</t>
   </si>
   <si>
+    <t>Our goal is to obtain two distinct groups of observations from a finite real-world dataset and construct a permutation distribution of a test statistic using a permutation-based approach.
+First, all observations from the two groups are combined into a single pooled dataset. Under the null hypothesis of no group difference, the group labels are exchangeable. Therefore, we randomly shuffle the labels and reassign the observations into two groups with new labels.
+We choose the sample mean difference as the test statistic,
+T = mean(Group 1)- mean(Group 2),
+since it is intuitive, computationally efficient, and well suited for a two-sided test. For each permutation, the test statistic is recalculated using the permuted labels, and this process is repeated n times (e.g., n = 1000 or n = 10000).
+We then visualize the resulting permutation distribution. In most cases, it is expected to be approximately symmetric and bell-shaped, and if the mean of the permutation statistics is close to zero, this is consistent with the null hypothesis. Finally, the permutation distribution is used to compute the p-value:
+p-value = (|T*| ≥ |T_observed| ) / n
+By comparing the observed test statistic to the permutation distribution, we can assess whether the observed result is a rare event under the null hypothesis. If the p-value is less than \alpha e.g., 0.05,  we reject the null hypothesis then conclude that there is a significant difference between the two groups.</t>
+  </si>
+  <si>
     <t>Extra details:</t>
   </si>
   <si>
+    <t>In Rcode implementation, the core function uses the sample() function to randomly shuffle the group labels, and a fixed random seed is set to ensure reproducibility when generating the permutation distribution.
+In the Shiny application, users can upload two groups of numerical data and adjust both the number of permutations and the significance level (0.01, 0.05, or 0.10). The default number of permutations is set to 10,000, as this allows for a more accurate estimation of the p-value.The interface then displays the results in real time, including boxplots of the permutation distribution, performs the hypothesis test, and provides an interpretation of the testing results.</t>
+  </si>
+  <si>
     <t>Topic Number 2</t>
   </si>
   <si>
@@ -71,6 +82,15 @@
     <t>Topic Number 3</t>
   </si>
   <si>
+    <t>High-dimensional feature selection via permutation test and bootstrap stability analysis</t>
+  </si>
+  <si>
+    <t>We generate synthetic datasets so that the true relevant features are known. To simulate real-world noise, we implement a mixture model f(x) = (1 - alpha) N(0,1) + alpha N(mu_{outlier}, sigma^2_{outlier}), where alpha represents the outlier proportion. Instead of standard Gaussian noise, we apply inverse-transform method to generate non-standard distributions to examine whether the hypothesis tests remain valid under complex conditions.</t>
+  </si>
+  <si>
+    <t>If a feature X is irrelevant to the outcome Y, shuffling / permuting Y should not significantly change the association between them. Hence, for each feature, we measure the association by mean difference and Kolmogorov-Smirnov statistic, and form a null distribution by repeatedly shuffling Y. We reject H0 if p&lt;0.05 and treat the feature as relevant, otherwise we fail to reject H0. To evaluate the stability, we repeatedly resample from the dataset and re-run the feature selection process. If the selected set of features changes across different bootstrap resamples, this process is unstable. Conversely, if similar features are selected every time, the process is stable. The Shiny application allows users to adjust the mixture strength and distribution type to visualize how the selected feature set changes across permutation statistics and bootstrap resampling.</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -134,6 +154,18 @@
     <t>Student 4</t>
   </si>
   <si>
+    <t>Liwen Yin</t>
+  </si>
+  <si>
+    <t>yinliwen</t>
+  </si>
+  <si>
+    <t>phoenixxxxxx77</t>
+  </si>
+  <si>
+    <t>https://github.com/phoenixxxxxxx77</t>
+  </si>
+  <si>
     <t>Student 5</t>
   </si>
   <si>
@@ -147,22 +179,19 @@
   </si>
   <si>
     <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
-  </si>
-  <si>
-    <t>High-dimensional feature selection via permutation test and bootstrap stability analysis</t>
-  </si>
-  <si>
-    <t>We generate synthetic datasets so that the true relevant features are known. To simulate real-world noise, we implement a mixture model f(x) = (1 - alpha) N(0,1) + alpha N(mu_{outlier}, sigma^2_{outlier}), where alpha represents the outlier proportion. Instead of standard Gaussian noise, we apply inverse-transform method to generate non-standard distributions to examine whether the hypothesis tests remain valid under complex conditions.</t>
-  </si>
-  <si>
-    <t>If a feature X is irrelevant to the outcome Y, shuffling / permuting Y should not significantly change the association between them. Hence, for each feature, we measure the association by mean difference and Kolmogorov-Smirnov statistic, and form a null distribution by repeatedly shuffling Y. We reject H0 if p&lt;0.05 and treat the feature as relevant, otherwise we fail to reject H0. To evaluate the stability, we repeatedly resample from the dataset and re-run the feature selection process. If the selected set of features changes across different bootstrap resamples, this process is unstable. Conversely, if similar features are selected every time, the process is stable. The Shiny application allows users to adjust the mixture strength and distribution type to visualize how the selected feature set changes across permutation statistics and bootstrap resampling.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -195,28 +224,166 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,8 +396,194 @@
         <bgColor rgb="FFC9DAF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -238,34 +591,319 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -463,27 +1101,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6607142857143" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.6607142857143" customWidth="1"/>
+    <col min="2" max="2" width="13.7767857142857" customWidth="1"/>
+    <col min="3" max="3" width="15.1071428571429" customWidth="1"/>
+    <col min="4" max="4" width="18.1071428571429" customWidth="1"/>
+    <col min="5" max="5" width="16.3303571428571" customWidth="1"/>
+    <col min="6" max="6" width="13.1071428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -491,7 +1128,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1">
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -499,7 +1136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -507,196 +1144,221 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+    <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:1">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:1">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:2">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:2">
+      <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:2">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:1">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:1">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:2">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:2">
+      <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="B16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:1">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+    <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>1009998237</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>1009834654</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D23">
         <v>1008554734</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+        <v>36</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24">
+        <v>1010276363</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:1">
       <c r="A25" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:1">
       <c r="A30" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F23" r:id="rId1" display="https://github.com/Togata1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>